--- a/moduli_aziende/shipping_service/moduli_compilati/MOD-720-G-Piano_Formazione_Annuale.xlsx
+++ b/moduli_aziende/shipping_service/moduli_compilati/MOD-720-G-Piano_Formazione_Annuale.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2000677752d934ed/INTERGLOBO/9001/Suite_9001_v4_viewerGUEST/moduli_compilati/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simoneleandrini\Documents\GitHub\SG_Viewer\moduli_aziende\shipping_service\moduli_compilati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_F4A6905C535E3AFF6438E0754C93FE7B31C7FF4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEF6F9D3-C797-40AE-91B1-3EE473609EB4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638AC0D5-DC6F-4A74-AEF8-BBCF24AB3856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="21">
   <si>
     <t>Anno</t>
   </si>
@@ -58,12 +58,6 @@
     <t>Sicurezza sul lavoro form generale e SQ aziendale</t>
   </si>
   <si>
-    <t>Q1/2026</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
     <t>RDF</t>
   </si>
   <si>
@@ -82,10 +76,13 @@
     <t>RDF + DIR</t>
   </si>
   <si>
-    <t>ok</t>
-  </si>
-  <si>
     <t>Attesa</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Q3/2026</t>
   </si>
 </sst>
 </file>
@@ -486,20 +483,20 @@
         <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -513,20 +510,20 @@
         <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -540,20 +537,20 @@
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -567,20 +564,20 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -594,20 +591,20 @@
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -621,20 +618,20 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -642,26 +639,26 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
         <v>19</v>
-      </c>
-      <c r="E8">
-        <v>4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -669,26 +666,26 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
         <v>19</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
